--- a/StructureDefinition-mii-pr-icu-score-icdsc.xlsx
+++ b/StructureDefinition-mii-pr-icu-score-icdsc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:46:19+00:00</t>
+    <t>2026-09-15T22:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -787,7 +787,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system= $loinc ).exists() or coding.where(system= $sct ).exists() or coding.where(system= $dgai).exists() or coding.where(system= $ieee-11073).exists()}</t>
+mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system='http://loinc.org').exists() or coding.where(system='http://snomed.info/sct').exists() or coding.where(system='urn:iso:std:iso:11073:10101').exists() or coding.where(system='http://dgai.de').exists()}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -978,7 +978,7 @@
     <t>Observation.code.coding:sct.version</t>
   </si>
   <si>
-    <t>http://snomed.info/sct/900000000000207008/version/20260301</t>
+    <t>http://snomed.info/sct/900000000000207008/version/20260701</t>
   </si>
   <si>
     <t>Observation.code.coding:sct.code</t>

--- a/StructureDefinition-mii-pr-icu-score-icdsc.xlsx
+++ b/StructureDefinition-mii-pr-icu-score-icdsc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T22:20:02+00:00</t>
+    <t>2026-09-17T12:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
